--- a/results/trace_ann29_greedy4096_results.xlsx
+++ b/results/trace_ann29_greedy4096_results.xlsx
@@ -930,7 +930,7 @@
         <v>82</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="F2">
         <v>1000</v>
@@ -1591,7 +1591,7 @@
         <v>67</v>
       </c>
       <c r="E31">
-        <v>37.10522622123899</v>
+        <v>37.83281242813555</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1602,7 +1602,7 @@
         <v>68</v>
       </c>
       <c r="E32">
-        <v>36.24469424768195</v>
+        <v>37.02425089792825</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1670,7 @@
         <v>82</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="I2">
         <v>1000</v>
